--- a/results/Int Task Remove ACC 0.7/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.7/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.00481335952848726 +/- 0.000977394339004535</t>
+          <t>-9.823182711194977e-05 +/- 0.0008450221283931854</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,362 +886,362 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.00034381139489196854 +/- 0.000933202357563832</t>
+          <t>-0.0010314341846757945 +/- 0.0011296660117878043</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0015717092337917738 +/- 0.0007545329811265818</t>
+          <t>0.0005893909626719318 +/- 0.0013857304498689595</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.001620825147347771 +/- 0.0012817277358251192</t>
+          <t>-0.0006385068762278512 +/- 0.001007774289228037</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0007367387033399009 +/- 0.000503288348033381</t>
+          <t>0.001620825147347771 +/- 0.0008233327413674181</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.005746561886051116 +/- 0.0017441336841419114</t>
+          <t>0.003634577603143463 +/- 0.0015717092337917357</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0001473477406680024 +/- 0.00044204322200392076</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.002996070726915534 +/- 0.001108105517944857</t>
+          <t>0.005500982318271152 +/- 0.0007858546168958868</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0033398821218074914 +/- 0.0026883953209045084</t>
+          <t>0.0036345776031434297 +/- 0.002252916491390908</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.002308447937131608 +/- 0.0026454288820226355</t>
+          <t>-0.0038310412573673625 +/- 0.002569095644522983</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0020137524557956588 +/- 0.0010636742547990136</t>
+          <t>-0.0018172888015716593 +/- 0.0010771960805236256</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0032907662082515164 +/- 0.000879983932572138</t>
+          <t>0.0013261296660118215 +/- 0.0008233327413674095</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.002799607072691568 +/- 0.001099362931512741</t>
+          <t>0.0035363457760314576 +/- 0.0007218535587769577</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.009037328094302532 +/- 0.0018920786133849081</t>
+          <t>-0.010412573673870306 +/- 0.002034608563576425</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.007662082514734736 +/- 0.00226359894337976</t>
+          <t>-0.003585461689587388 +/- 0.001825236166607287</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.00810412573673871 +/- 0.0008577725538592034</t>
+          <t>0.0075147347740668335 +/- 0.001584701945471674</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0006385068762279067 +/- 0.0009587043858518096</t>
+          <t>0.001719056974459765 +/- 0.0007367387033398972</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.002897838899803573 +/- 0.0011508226437976605</t>
+          <t>0.0004911591355599487 +/- 0.0008786121719056103</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.006385068762278967 +/- 0.0011413506914167149</t>
+          <t>0.003781925343811421 +/- 0.0013726118479844762</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>4.911591355599709e-05 +/- 0.00014734774066799128</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0011787819253438303 +/- 0.0014437071175539328</t>
+          <t>0.0012278978388998384 +/- 0.0017330332774437617</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0030451866404715535 +/- 0.0007218535587769939</t>
+          <t>0.0008349705304518951 +/- 0.0009835454024803832</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.001277013752455769 +/- 0.0009872176445108953</t>
+          <t>-0.0021611001964635945 +/- 0.0008277160877383434</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.0003929273084479101 +/- 0.0005727850584327489</t>
+          <t>-0.0003929273084479101 +/- 0.00048123570585131294</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0006876227897838593 +/- 0.0005469316662897873</t>
+          <t>-4.911591355596379e-05 +/- 0.0005578495428094478</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0007858546168958314 +/- 0.0003257981130015222</t>
+          <t>-0.00024557956777992995 +/- 0.0005914339184082748</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0007367387033398898 +/- 0.001427744779346619</t>
+          <t>-0.0007858546168958425 +/- 0.0011455701168654683</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.005844793713163066 +/- 0.0013078120781625025</t>
+          <t>0.00029469548133597144 +/- 0.0013575908606174066</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.003781925343811421 +/- 0.0011838871113157045</t>
+          <t>0.002111984282907697 +/- 0.0016590712921468068</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0014243614931237936 +/- 0.000834970530451878</t>
+          <t>0.00014734774066799128 +/- 0.0007301605475107236</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-4.911591355598599e-05 +/- 0.00014734774066795797</t>
+          <t>-0.00039292730844788795 +/- 0.00019646365422394397</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>-0.0003929273084479101 +/- 0.0003675498415298463</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-4.911591355595268e-05 +/- 0.0005127851919897154</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.001669941060903768 +/- 0.0009624714117026291</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
           <t>0.00014734774066799128 +/- 0.00022507739169726432</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.0014734774066797796 +/- 0.0006212726247875021</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.003732809430255446 +/- 0.0009872176445108875</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.0004420432220039627 +/- 0.0005127851919897101</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.00029469548133592705 +/- 0.00032579811300149534</t>
+          <t>-0.0007858546168958425 +/- 0.00039292730844793516</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-9.823182711194977e-05 +/- 0.0005727850584327299</t>
+          <t>-0.002455795677799555 +/- 0.0010302640944696844</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0013752455795678076 +/- 0.0003675498415298493</t>
+          <t>0.00029469548133598256 +/- 0.0005893909626719004</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0004911591355599376 +/- 0.0005811473264341399</t>
+          <t>-0.0010314341846758058 +/- 0.0005127851919897027</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.0011787819253437858 +/- 0.0012464221552504612</t>
+          <t>-0.0020628683693516225 +/- 0.001071582722459303</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.001227897838899783 +/- 0.0012080917363702225</t>
+          <t>0.0008840864440079032 +/- 0.0008731035773394694</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0015717092337917404 +/- 0.000651596226003041</t>
+          <t>0.0015225933202357989 +/- 0.0005578495428094743</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0022593320235756555 +/- 0.0007672150958651171</t>
+          <t>0.002357563850687672 +/- 0.001332481332637575</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.009184675834970513 +/- 0.0009069835615235377</t>
+          <t>-0.01380157170923375 +/- 0.0015130571513506186</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-4.911591355597489e-05 +/- 0.0012512513951725935</t>
+          <t>-0.004469548133595247 +/- 0.0015907794440767867</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0002455795677799966 +/- 0.0008291720538376372</t>
+          <t>-0.0021611001964635832 +/- 0.0011869396830642789</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.0007858546168958425 +/- 0.00024061785292568027</t>
+          <t>0.0001473477406680024 +/- 0.0004420432220039208</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.0011296660117877777 +/- 0.0009332023575638582</t>
+          <t>-0.0006876227897838372 +/- 0.000884086444007833</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.003831041257367396 +/- 0.0012770137524557843</t>
+          <t>0.000785854616895898 +/- 0.0009109644887520418</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.006483300589390973 +/- 0.0010715827224593083</t>
+          <t>-0.001424361493123727 +/- 0.0009434858896020883</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0019155206286837311 +/- 0.001590779444076794</t>
+          <t>0.0032907662082515055 +/- 0.0013726118479844662</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
+          <t>-0.0010314341846757945 +/- 0.0003438113948919368</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>-0.0009332023575638115 +/- 0.0005578495428094528</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.002554027504911638 +/- 0.0009773943390045353</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.008447937131630678 +/- 0.00219433279996943</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.00034381139489197965 +/- 0.0007301605475107236</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>0.00019646365422398837 +/- 0.00024061785292568027</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>4.91159135560193e-05 +/- 0.0007100605252849128</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.00039292730844796563 +/- 0.0005289945783039786</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.002161100196463672 +/- 0.0015249680448192564</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.0026522593320235876 +/- 0.0011026495245895734</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.00019646365422398837 +/- 0.00024061785292568027</t>
-        </is>
-      </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-0.00024557956777994107 +/- 0.0004528263485900214</t>
+          <t>-0.0022593320235755774 +/- 0.000666240666318787</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.0004911591355598821 +/- 0.0009319089371812515</t>
+          <t>-0.0021119842829076087 +/- 0.0012627662212360122</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.0008840864440078144 +/- 0.000481235705851322</t>
+          <t>-0.0006385068762278622 +/- 0.0005402750491158943</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.00034381139489196854 +/- 0.0006232110776252122</t>
+          <t>4.911591355600819e-05 +/- 0.000805560877546983</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.002996070726915534 +/- 0.0007100605252849188</t>
+          <t>-9.823182711194977e-05 +/- 0.0008450221283931853</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.004518664047151244 +/- 0.0007858546168958688</t>
+          <t>-0.005943025540275005 +/- 0.0019701543340011223</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-9.823182711196087e-05 +/- 0.00029469548133593816</t>
+          <t>-0.00019646365422393286 +/- 0.00045015478339448017</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>9.823182711199419e-05 +/- 0.00019646365422398837</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.0010805500982317916 +/- 0.0009267172035418912</t>
+          <t>-0.0014734774066797352 +/- 0.0006946039107922857</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.00039292730844788795 +/- 0.0007218535587769607</t>
+          <t>-0.001375245579567741 +/- 0.0006515962260030226</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.0004911591355598932 +/- 0.0004911591355599042</t>
+          <t>0.0004420432220039516 +/- 0.0006752321750917348</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.0024557956777996326 +/- 0.0005380378757418271</t>
+          <t>-0.0004420432220038961 +/- 0.0005578495428094479</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.0021119842829076417 +/- 0.0005832191594812391</t>
+          <t>0.0007858546168958869 +/- 0.0007015155627252519</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.002504911591355574 +/- 0.001086117111370138</t>
+          <t>-0.00137524557956773 +/- 0.0006876227897838768</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-9.823182711196087e-05 +/- 0.00029469548133593816</t>
+          <t>3.3306690738754695e-17 +/- 0.0003804502304722367</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9.823182711200529e-05 +/- 0.0005289945783039786</t>
+          <t>0.00024557956777997435 +/- 0.0004528263485900154</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.0004420432220039516 +/- 0.00046335860177096203</t>
+          <t>0.000540275049115957 +/- 0.00014734774066795797</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.00014734774066799128 +/- 0.0007934918674559519</t>
+          <t>-0.0016699410609036791 +/- 0.0007350996830597059</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.00019646365422393286 +/- 0.000450154783394456</t>
+          <t>4.91159135560193e-05 +/- 0.00034381139489194474</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0005893909626719207 +/- 0.0005727850584327299</t>
+          <t>-0.0006876227897838593 +/- 0.0005469316662897874</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.00019646365422393286 +/- 0.0007672150958650857</t>
+          <t>0.0014734774066798018 +/- 0.0004911591355599708</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.00044204322200388504 +/- 0.000264497289151979</t>
+          <t>4.91159135560304e-05 +/- 0.0004079874195932227</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.0006876227897838483 +/- 0.0005008860032998659</t>
+          <t>-0.00034381139489192414 +/- 0.0003836075479325358</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.0011296660117877887 +/- 0.0009587043858518404</t>
+          <t>-0.0038310412573673513 +/- 0.0009267172035419077</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0006385068762279178 +/- 0.0005402750491159196</t>
+          <t>-0.0007367387033398343 +/- 0.0006309053329403379</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.00025759917568263235 +/- 0.00025759917568263235</t>
+          <t>0.001648634724368847 +/- 0.0005047892308672079</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,27 +1331,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.00015455950540957942 +/- 0.0008323284091397821</t>
+          <t>0.0007212776919113706 +/- 0.0003417439248176537</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0015971148892323205 +/- 0.0004860371526046576</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5.151983513652647e-05 +/- 0.000277442803046594</t>
+          <t>0.0015971148892323205 +/- 0.0004279558919586759</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.0005667181865017911 +/- 0.0006697578567748441</t>
+          <t>0.000978876867594003 +/- 0.0004860371526046576</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.0014425553838227413 +/- 0.0005548856060931881</t>
+          <t>-0.001030396702730607 +/- 0.0003990709269662805</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1361,402 +1361,402 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.00010303967027305294 +/- 0.0003855391434079199</t>
+          <t>0.0010819165378670558 +/- 0.00036063884595568526</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.007573415765069558 +/- 0.002471341567276957</t>
+          <t>0.0003606388459556742 +/- 0.0007658974109901382</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.0038124678001030476 +/- 0.001680526164894388</t>
+          <t>0.006594538897475499 +/- 0.002146591103142696</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.00041215868109221174 +/- 0.0005047892308672079</t>
+          <t>0.0013395157135496882 +/- 0.0004121586810922118</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.00030911901081915883 +/- 0.0005254012893964634</t>
+          <t>-0.00010303967027306405 +/- 0.00044913950989601277</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>0.0022153529108706383 +/- 0.0005177679351427447</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.000978876867594003 +/- 0.0006697578567748441</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.013910355486862414 +/- 0.002136676079683433</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>-0.0003091190108191921 +/- 0.000573700604104102</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.0012364760432766353 +/- 0.0004721870886095562</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.00030911901081915883 +/- 0.00047218708860955616</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.0015971148892323205 +/- 0.0004279558919586758</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>5.151983513652647e-05 +/- 0.00015455950540957942</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-0.0006697578567748885 +/- 0.00032988790507128567</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.00041215868109221174 +/- 0.0004491395098959898</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.00020607934054610587 +/- 0.00025239461543360395</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.0007212776919113706 +/- 0.00034174392481765376</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.0005151983513652647 +/- 0.0003990709269662375</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.00087583719732095 +/- 0.0008323284091397821</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>-0.00041215868109221174 +/- 0.0002060793405461059</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>5.151983513651537e-05 +/- 0.00042795589195870394</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>-0.0007727975270479415 +/- 0.00047498941047365413</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.0006697578567748441 +/- 0.0004023827756778201</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-0.0007212776919114261 +/- 0.0006597758101425263</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.0004636785162287382 +/- 0.0005378828701138758</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.00015455950540957942 +/- 0.0002360935443047781</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.0011334363730035823 +/- 0.0005047892308672079</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.00010303967027305294 +/- 0.0004491395098959898</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>5.151983513652647e-05 +/- 0.00015455950540957942</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.00010303967027305294 +/- 0.00020607934054610587</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-5.151983513652647e-05 +/- 0.00015455950540957942</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>-0.00046367851622876045 +/- 0.0004860371526046953</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-0.002524471921689897 +/- 0.0013718214276861643</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>-0.00020607934054613918 +/- 0.0008047655513556815</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.00020607934054610587 +/- 0.00025239461543360395</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0012364760432766353 +/- 0.0005254012893964634</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.001184956208140109 +/- 0.0005177679351427448</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>-0.0022153529108707493 +/- 0.0008636298101102449</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-0.0020607934054611586 +/- 0.0014388706897237261</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-0.00010303967027307515 +/- 0.0006434825346108786</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>-0.00025759917568264347 +/- 0.00034560556066459084</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>-0.0035548686244204373 +/- 0.0015702988824449094</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-0.0022668727460072647 +/- 0.0011793429306810469</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.00015455950540957942 +/- 0.00032988790507123715</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.0007727975270478971 +/- 0.0004153661900205244</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-0.003194229778464752 +/- 0.0012577594658148836</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.00020607934054610587 +/- 0.00025239461543360395</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.0017001545595053736 +/- 0.0007998029209819523</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-0.0030396702730551726 +/- 0.0005378828701138758</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.001957753735188006 +/- 0.00044913950989598983</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-0.000618238021638362 +/- 0.0003855391434079673</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>-0.00010303967027305294 +/- 0.00044913950989598983</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.0017001545595053736 +/- 0.0006537134230009918</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.00015455950540957942 +/- 0.0002360935443047781</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>0.00041215868109221174 +/- 0.00030911901081915883</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.002060793405461103 +/- 0.0014753035613886104</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.01916537867078828 +/- 0.0027046686756118823</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-0.00015455950540957942 +/- 0.0002360935443047781</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0016486347243688582 +/- 0.0005047892308672282</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>-0.00025759917568263235 +/- 0.000345605560664566</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.00041215868109221174 +/- 0.0002060793405461059</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-0.00030911901081915883 +/- 0.0005254012893964634</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.00025759917568263235 +/- 0.00025759917568263235</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0003606388459556853 +/- 0.00023609354430477808</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-0.0009273570324575431 +/- 0.0003855391434079673</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-0.002369912416280329 +/- 0.0006182380216383177</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.0006697578567748441 +/- 0.0003298879050712371</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.00025759917568263235 +/- 0.000345605560664566</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>-0.0013395157135497882 +/- 0.00047218708860957557</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>0.0013395157135496882 +/- 0.0006597758101424743</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
         <is>
           <t>0.00010303967027305294 +/- 0.0002060793405461059</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>-0.00020607934054610587 +/- 0.00025239461543360395</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>-0.0006182380216383177 +/- 0.00030911901081915883</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.0004636785162287382 +/- 0.00042795589195867586</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-0.002163833075734134 +/- 0.0006008193606229273</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-0.0008243173621844235 +/- 0.0003417439248176537</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>-0.00025759917568263235 +/- 0.00025759917568263235</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.00015455950540957942 +/- 0.0003298879050712371</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>5.151983513652647e-05 +/- 0.000277442803046594</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.0025244719216898303 +/- 0.0004860371526046964</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.00025759917568263235 +/- 0.000345605560664566</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-0.0012879958784131728 +/- 0.0015326609768823664</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.00010303967027305294 +/- 0.00030911901081915883</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.00020607934054610587 +/- 0.00025239461543360395</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0003606388459556853 +/- 0.00023609354430477808</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.00030911901081915883 +/- 0.00025239461543360395</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.0005667181865017911 +/- 0.0004860371526046576</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.00020607934054610587 +/- 0.00025239461543360395</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.00041215868109221174 +/- 0.0007571838463008118</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-0.00010303967027305294 +/- 0.0004491395098959898</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>5.151983513652647e-05 +/- 0.00015455950540957942</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-0.003863987635239574 +/- 0.001036816681993731</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.0008243173621844235 +/- 0.00025239461543360395</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.00010303967027305294 +/- 0.00020607934054610587</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.00025759917568263235 +/- 0.00025759917568263235</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-0.0021123132405976076 +/- 0.0009056360551904835</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>5.151983513652647e-05 +/- 0.000277442803046594</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-0.0028335909325090114 +/- 0.0009569384657911997</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.002215352910870694 +/- 0.0009230537283446388</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.0003606388459556853 +/- 0.00023609354430477808</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>-0.00020607934054610587 +/- 0.00034174392481765376</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.00015455950540957942 +/- 0.0002360935443047781</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>5.151983513652647e-05 +/- 0.00015455950540957942</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.0004636785162287382 +/- 0.00015455950540957942</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-0.00030911901081915883 +/- 0.0004121586810922118</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.00010303967027305294 +/- 0.00020607934054610587</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.0006182380216383177 +/- 0.00030911901081915883</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.00030911901081915883 +/- 0.00025239461543360395</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>5.151983513652647e-05 +/- 0.00015455950540957942</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>5.151983513652647e-05 +/- 0.00015455950540957942</t>
-        </is>
-      </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0003606388459556853 +/- 0.00023609354430477808</t>
+          <t>-0.0013910355486863146 +/- 0.0004023827756778443</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.0005667181865017911 +/- 0.000277442803046594</t>
+          <t>0.0017001545595053736 +/- 0.000978876867594003</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.00010303967027305294 +/- 0.00030911901081915883</t>
+          <t>0.0010303967027305294 +/- 0.0002304037071097107</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.000889586603872361 +/- 0.0008453947891890888</t>
+          <t>0.0023024594453165846 +/- 0.0010254274171776789</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,282 +1776,282 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.0015175300889585853 +/- 0.0005943389163579495</t>
+          <t>-0.000680272108843516 +/- 0.0007779209182270408</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.001988487702773345 +/- 0.0007326007326007331</t>
+          <t>0.0001569858712716088 +/- 0.0010214139872288378</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.0014652014652014045 +/- 0.0008038875717287809</t>
+          <t>-0.0005232862375719183 +/- 0.0008106715533662955</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.00026164311878602576 +/- 0.0007117462327962065</t>
+          <t>0.0006279434850863686 +/- 0.0005635965261260733</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.00209314495028774 +/- 0.001516627602950243</t>
+          <t>0.0013082155939299067 +/- 0.0010267617409915495</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00041862899005761233 +/- 0.00031397174254319535</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.00444793301936155 +/- 0.0013494292996575176</t>
+          <t>0.0013082155939299067 +/- 0.0008190725192306751</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.016431187859759354 +/- 0.002555009024748013</t>
+          <t>0.020251177394034557 +/- 0.001736332812458102</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.011355311355311403 +/- 0.002668759811616953</t>
+          <t>0.024123495552066998 +/- 0.003028285985605482</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.002511773940345419 +/- 0.0009002956846721734</t>
+          <t>0.0028257456828885696 +/- 0.0011271930522521168</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.0002093144950287451 +/- 0.0007098199877681978</t>
+          <t>-0.00010465724751436145 +/- 0.001117433621353343</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.0008372579801150693 +/- 0.000817399233480533</t>
+          <t>0.0017268445839874636 +/- 0.0008453947891890661</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.00905285190999483 +/- 0.0010478798741235505</t>
+          <t>0.018890633176347503 +/- 0.0016948335678389863</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.012401883830455318 +/- 0.001405099066676869</t>
+          <t>0.009576138147566738 +/- 0.0009078676908894402</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.002040816326530559 +/- 0.0012482323853350691</t>
+          <t>-0.00031397174254313984 +/- 0.0007831831264832936</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.0010465724751438476 +/- 0.000843773704688487</t>
+          <t>0.0027210884353741638 +/- 0.00114167578384467</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.000889586603872261 +/- 0.0011476563160367059</t>
+          <t>0.0035583464154892996 +/- 0.0012987622863412857</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.0006802721088434938 +/- 0.0005756148613291101</t>
+          <t>0.0008895866038723388 +/- 0.0007779209182270237</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>0.00010465724751441696 +/- 0.00031397174254319535</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.007796964939822082 +/- 0.0013735640762330375</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-0.002197802197802168 +/- 0.001117433621353346</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.0014652014652014821 +/- 0.0008372579801151108</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.0007849293563578996 +/- 0.0005362088312904009</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.0007849293563579774 +/- 0.00042188685234424</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.00010465724751435035 +/- 0.0006535843012452526</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.005599162742019914 +/- 0.0020273543304877573</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.0029304029304029534 +/- 0.0008502394981304166</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.0006279434850863907 +/- 0.0012987622863412666</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.005494505494505508 +/- 0.0011759395632780925</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>-0.0008372579801150803 +/- 0.0003471088215965893</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-0.0012558869701726593 +/- 0.0007098199877682157</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.0062794348508634305 +/- 0.0017036965563683624</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.0010465724751439255 +/- 0.001587205744437796</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2.2204460492503132e-17 +/- 0.0006619105515789313</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>-0.001831501831501814 +/- 0.0007117462327962106</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.004918890633176376 +/- 0.0009419152276295244</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-0.0007326007326006967 +/- 0.0004795997587604114</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.005023547880690771 +/- 0.0014273345575076906</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.004814233385661992 +/- 0.0013805239098140145</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.006122448979591855 +/- 0.001047879874123531</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0001569858712716199 +/- 0.0014244539601063584</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.0036106750392465026 +/- 0.0020727684270369982</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.0009942438513867446 +/- 0.0011571608784665616</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>-0.0016745159602302273 +/- 0.0013402667163648233</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>-0.00036630036630034277 +/- 0.000239799879380196</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>-0.011512297226582913 +/- 0.0018426809902311997</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.0013082155939299067 +/- 0.0017706880497842573</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.00020931449502881172 +/- 0.0015381411257665027</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.007326007326007344 +/- 0.0026682467365739247</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-0.0005756148613291212 +/- 0.00043467419481517676</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>-0.00010465724751438366 +/- 0.00020931449502876732</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
           <t>5.232862375720293e-05 +/- 0.0001569858712716088</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.003139717425431776 +/- 0.0007400384941774434</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.003506017791732141 +/- 0.0005258961601842516</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.0006279434850863796 +/- 0.0006535843012452526</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.0016221873364730022 +/- 0.0005463268712145889</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.001988487702773456 +/- 0.0009302139630890294</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.0006802721088434938 +/- 0.0004086996167402487</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.003558346415489333 +/- 0.0006535843012452579</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>5.551115123125783e-17 +/- 0.0010200726682165347</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>0.003192046049188968 +/- 0.0007565061378755026</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.0006279434850864019 +/- 0.0010672986946295602</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.00057561486132921 +/- 0.0005943389163579485</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.0007326007326006855 +/- 0.00041862899005753464</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-0.0010465724751438366 +/- 0.000810671553366274</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.0030350601779173814 +/- 0.0009302139630890267</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0.00020931449502881172 +/- 0.0002563568542944574</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.0014128728414443236 +/- 0.0005756148613291495</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>-0.0047619047619047224 +/- 0.0010052000372736051</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0.002145473574045054 +/- 0.0008582532426403388</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-0.0002093144950287451 +/- 0.0007831831264832802</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.0038199895342752145 +/- 0.001194423046626211</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.00026164311878595914 +/- 0.0004824460731183828</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.3306690738754695e-17 +/- 0.0009063583503761653</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0029304029304029868 +/- 0.0008818576424046438</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>-0.005389848246991069 +/- 0.0006639758001281689</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>-0.002040816326530559 +/- 0.001058280921829248</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>-0.01004709576138143 +/- 0.0016009480419443662</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>-0.0005232862375719183 +/- 0.00046804143956036547</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>-0.011983254840397629 +/- 0.00197813272333185</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>-0.0037153322867608087 +/- 0.0011805875638596192</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-0.0017268445839873857 +/- 0.0007779209182270267</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>0.002721088435374208 +/- 0.0011174336213533554</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0.00010465724751441696 +/- 0.00031397174254319535</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.00057561486132921 +/- 0.0004346741948151794</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.000523286237571996 +/- 0.0004680414395604027</t>
-        </is>
-      </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.003453689167974938 +/- 0.0013484143094427386</t>
+          <t>0.0008372579801151581 +/- 0.0016247173936430963</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.0015698587127157882 +/- 0.0004680414395604027</t>
+          <t>-0.007744636316064868 +/- 0.0009873344983837356</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.0006802721088435715 +/- 0.0005756148613291495</t>
+          <t>-0.0002093144950287451 +/- 0.00047959975876042595</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-0.002878074306645673 +/- 0.0011759395632780826</t>
+          <t>-0.002197802197802168 +/- 0.0009873344983837558</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.00010465724751435035 +/- 0.0011886778327159031</t>
+          <t>0.008058608058608063 +/- 0.002069463101338068</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
+          <t>-0.0007326007326006855 +/- 0.0003471088215965659</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-0.004971219256933524 +/- 0.0011759395632780778</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.008581894296180026 +/- 0.0017699146546612194</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.00041862899005759016 +/- 0.0008372579801151179</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-0.00015698587127154217 +/- 0.0006639758001281803</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
           <t>-0.00010465724751438366 +/- 0.00020931449502876732</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-0.007535321821036056 +/- 0.0011978569484311387</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.0007326007326007855 +/- 0.0010775123119818974</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-0.0037153322867607974 +/- 0.0011332500171485052</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-0.0006279434850863019 +/- 0.00039159156324162234</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.004133961276818377 +/- 0.0011805875638596077</t>
+          <t>-0.0037153322867608416 +/- 0.0012699802301948122</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.0012035583464154343 +/- 0.0014050990666768788</t>
+          <t>-5.232862375715852e-05 +/- 0.0008257317550005096</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.003349031920460421 +/- 0.0008502394981304112</t>
+          <t>-0.001046572475143881 +/- 0.0005232862375719627</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.0028257456828884807 +/- 0.0009983665111637234</t>
+          <t>-0.001779173207744611 +/- 0.0012645783331862686</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0015175300889586963 +/- 0.0008582532426403382</t>
+          <t>0.00026164311878601465 +/- 0.0006721733426826381</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-0.00041862899005752353 +/- 0.0012558869701726908</t>
+          <t>-0.0005756148613291323 +/- 0.000825731755000506</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.000156985871271631 +/- 0.00040869961674029853</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>5.2328623757236235e-05 +/- 0.0005943389163579633</t>
+          <t>0.0008372579801151691 +/- 0.0003471088215965927</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-5.2328623757169625e-05 +/- 0.00043467419481518077</t>
+          <t>-5.2328623757169625e-05 +/- 0.0004936672491918743</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.0003663003663004094 +/- 0.00033506667909122793</t>
+          <t>-0.0009942438513866891 +/- 0.0008257317550005103</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-0.0016745159602302051 +/- 0.0012775045123740174</t>
+          <t>-0.00047095761381471535 +/- 0.0009491552667303654</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00041862899005761233 +/- 0.00031397174254319535</t>
+          <t>-0.0011512297226582869 +/- 0.0006942176431931803</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.00020931449502881172 +/- 0.0004186289900575818</t>
+          <t>0.00010465724751442806 +/- 0.0008372579801151193</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0006802721088435048 +/- 0.0008771875779298855</t>
+          <t>-0.0024071166928309575 +/- 0.001220502751406639</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.0006279434850863686 +/- 0.0006102513757033347</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.002354788069073721 +/- 0.0006721733426826251</t>
+          <t>-0.0012558869701726483 +/- 0.0007831831264832922</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.00010465724751436145 +/- 0.0008038875717288012</t>
+          <t>-0.002982731554160101 +/- 0.0011944230466261925</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.0003663003663003983 +/- 0.0006639758001281856</t>
+          <t>-0.0002093144950287229 +/- 0.0007831831264833159</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.008501594048884098 +/- 0.0008231633041886124</t>
+          <t>-0.008342189160467606 +/- 0.0007533181125801188</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,27 +2221,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.001912858660998862 +/- 0.00138965959942847</t>
+          <t>-0.007226354941551561 +/- 0.0010679995346568544</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.005632306057385716 +/- 0.0009855067476615955</t>
+          <t>-0.006535600425079724 +/- 0.001090238285264804</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.002337938363443204 +/- 0.0014098298790033556</t>
+          <t>0.003134962805525998 +/- 0.0010206893045854703</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.007226354941551494 +/- 0.0012618854502697127</t>
+          <t>-0.004197662061636576 +/- 0.0006485948786255812</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.016099893730074345 +/- 0.0012128280776315982</t>
+          <t>-0.004197662061636576 +/- 0.0014734776433434666</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2251,127 +2251,127 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.013230605738575929 +/- 0.0015113137782495018</t>
+          <t>-0.008182784272051014 +/- 0.0012840643967688336</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0037725823591924002 +/- 0.0021837112208325776</t>
+          <t>0.0019128586609989061 +/- 0.004735872466558383</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.0006376195536663576 +/- 0.0013400127750179014</t>
+          <t>-0.0009032943676939742 +/- 0.003318702756562619</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0035069075451647836 +/- 0.0007589190678578997</t>
+          <t>0.004410201912858636 +/- 0.0008584215951861743</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.000850159404888351 +/- 0.0008954463095830235</t>
+          <t>-0.0004250797024442199 +/- 0.000850159404888412</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.005791710945802264 +/- 0.0009926430229686334</t>
+          <t>-0.014080765143464435 +/- 0.0021419388279220438</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.012221041445271053 +/- 0.0019304890674372883</t>
+          <t>0.0070138150903293894 +/- 0.0016769111411328056</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.001912858660998884 +/- 0.0014297156266815801</t>
+          <t>0.008395324123273085 +/- 0.0011592680249347075</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.0004250797024441533 +/- 0.0008162747872336434</t>
+          <t>-0.007704569606801303 +/- 0.0012404481965917846</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.01206163655685435 +/- 0.0013026196250936486</t>
+          <t>-0.008554729011689721 +/- 0.0014541904551970113</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0013815090329437284 +/- 0.0005418724243988067</t>
+          <t>0.007492029755579143 +/- 0.0008384555705664113</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.012167906482465397 +/- 0.0021180798541971155</t>
+          <t>-0.007173219978746037 +/- 0.0012630036476094354</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.0003719447396386633 +/- 0.00024349498910497378</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0011158342189161008 +/- 0.0008040778932211197</t>
+          <t>0.0017003188097768017 +/- 0.001421794703534478</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0033475026567481693 +/- 0.0015771330584118956</t>
+          <t>-0.00010626992561106885 +/- 0.0012301633265451863</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.000690754516471892 +/- 0.0008248764450722628</t>
+          <t>-0.0006907545164718698 +/- 0.000951991119403239</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0019128586609989506 +/- 0.0003524574697508215</t>
+          <t>0.005313496280552577 +/- 0.0012574027169181062</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.002231668437832135 +/- 0.0005722810634574534</t>
+          <t>0.00951115834218913 +/- 0.0008040778932211351</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>5.3134962805534426e-05 +/- 0.00015940488841660326</t>
+          <t>0.00031880977683313995 +/- 0.0004250797024441866</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0035600425079702846 +/- 0.0019602408868965625</t>
+          <t>0.009404888416578083 +/- 0.0011408560336654513</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.0023379383634430707 +/- 0.001716843190372314</t>
+          <t>0.004091392136025463 +/- 0.002044833305514763</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.0034006376195536148 +/- 0.0016325495744672794</t>
+          <t>0.002337938363443115 +/- 0.001700318809776808</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0032412327311371336 +/- 0.00093402740867413</t>
+          <t>-0.0009564293304994753 +/- 0.0018065887353878778</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00010626992561105775 +/- 0.00031880977683317323</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.0008501594048883731 +/- 0.0002603070927505901</t>
+          <t>0.00031880977683313995 +/- 0.0002603070927505901</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0016471838469713674 +/- 0.0015842775255978142</t>
+          <t>-2.2204460492503132e-17 +/- 0.0011145683827525588</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.0039851222104143715 +/- 0.0008970214142473073</t>
+          <t>0.008289054197662038 +/- 0.001192876956463536</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.00015940488841660329 +/- 0.00024349498910502463</t>
+          <t>-0.0005313496280552443 +/- 0.000237626777630171</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.0007438894792774154 +/- 0.0006804595363903115</t>
+          <t>0.00010626992561103554 +/- 0.0006636554727309526</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.00021253985122207108 +/- 0.0015618425565036155</t>
+          <t>0.006376195536663076 +/- 0.001164128708831375</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.0017534537725822918 +/- 0.0011653407119798511</t>
+          <t>0.004357066950053079 +/- 0.0017102525971765081</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.0002656748140275944 +/- 0.0004898801518221624</t>
+          <t>0.00015940488841656997 +/- 0.00047821466524970995</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.0033475026567480804 +/- 0.0008248764450722584</t>
+          <t>0.00021253985122209328 +/- 0.00042507970244418656</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.001965993623804496 +/- 0.0009218571505258906</t>
+          <t>-0.004888416578108434 +/- 0.0012971897572511915</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0006907545164718809 +/- 0.0012358877098419805</t>
+          <t>-0.0002125398512221155 +/- 0.0005916859046578148</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.0028161530286928025 +/- 0.0011653407119798856</t>
+          <t>-0.003134962805526065 +/- 0.001267466571931621</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.00940488841657804 +/- 0.0014267504338041968</t>
+          <t>0.00494155154091388 +/- 0.0013660956569800686</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.002816153028692814 +/- 0.0008248764450722648</t>
+          <t>-0.0005313496280552777 +/- 0.0005820643544157129</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.002284803400637658 +/- 0.0008584215951861619</t>
+          <t>0.00010626992561102444 +/- 0.000816274787233636</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.0004782146652497099 +/- 0.0003719447396386632</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0012752391073326819 +/- 0.0010137504797204564</t>
+          <t>-0.0006376195536663465 +/- 0.0011833718093156097</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.0023379383634430707 +/- 0.0007207577027763377</t>
+          <t>0.0017003188097767796 +/- 0.0008162747872336433</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.003294367693942657 +/- 0.0016769111411327872</t>
+          <t>-0.004782146652497365 +/- 0.0014648298355037367</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.004835281615302789 +/- 0.0016540257615593418</t>
+          <t>5.313496280550112e-05 +/- 0.0012221041445270953</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.0010095642933049432 +/- 0.00015940488841656997</t>
+          <t>0.0004782146652497099 +/- 0.0004413721499956244</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-0.00031880977683313995 +/- 0.0002603070927505901</t>
+          <t>0.00031880977683313995 +/- 0.0002603070927505901</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.0024973432518596516 +/- 0.0013452698088386988</t>
+          <t>-0.004941551540913936 +/- 0.0015224812733150182</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.0044102019128585915 +/- 0.0010902382852647737</t>
+          <t>0.0037725823591923334 +/- 0.0013112606460417733</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.0009564293304994198 +/- 0.0013609190727806222</t>
+          <t>-0.0012752391073326485 +/- 0.001192876956463548</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.0005844845908607565 +/- 0.0004413721499956244</t>
+          <t>0.00031880977683312883 +/- 0.0006376195536663039</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.0021785334750265227 +/- 0.0011507124244265368</t>
+          <t>-0.0030818278427205193 +/- 0.0009739799564199374</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.004038257173220006 +/- 0.0007207577027763212</t>
+          <t>0.005738575982996774 +/- 0.0018065887353879027</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0004250797024441755 +/- 0.00046321986647616015</t>
+          <t>-0.0014877789585547641 +/- 0.0006196548241068015</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.00010626992561109105 +/- 0.0010025484731197212</t>
+          <t>0.004729011689691765 +/- 0.001198779401984947</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.0002125398512221599 +/- 0.0010941158492015846</t>
+          <t>0.006695005313496249 +/- 0.0011689691817215696</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.001912858660998873 +/- 0.002114744818505036</t>
+          <t>0.00037194473963865217 +/- 0.001916545036861992</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.002072263549415443 +/- 0.0007681632462699781</t>
+          <t>-0.000903294367693952 +/- 0.0006742070956668321</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-0.0006376195536662687 +/- 0.0005206141855012052</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.0003188097768331066 +/- 0.0010679995346568314</t>
+          <t>-0.004516471838469737 +/- 0.0010693204993356992</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.0013815090329436063 +/- 0.0005916859046577829</t>
+          <t>0.0010626992561104665 +/- 0.0005820643544156623</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.000531349628055311 +/- 0.0004115816520943277</t>
+          <t>0.0006907545164718032 +/- 0.0005844845908607566</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.0010626992561105554 +/- 0.0009203245523745278</t>
+          <t>0.0012221041445270586 +/- 0.0007899080099531469</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.0017003188097767462 +/- 0.0005722810634574101</t>
+          <t>0.0015940488841657441 +/- 0.0010357911099690641</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.0013815090329437284 +/- 0.0009564293304994716</t>
+          <t>-0.003931987247608959 +/- 0.001429715626681584</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-0.00010626992561103554 +/- 0.0003188097768331621</t>
+          <t>-0.0005313496280552332 +/- 0.0</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.0006376195536662799 +/- 0.00046321986647613716</t>
+          <t>0.0010626992561104775 +/- 0.0005313496280552556</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.00010626992561104664 +/- 0.00021253985122209328</t>
+          <t>0.00021253985122209328 +/- 0.0002603070927505901</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.00015940488841656997 +/- 0.00024349498910497378</t>
+          <t>-0.0006376195536663242 +/- 0.00039762565215453743</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.00010626992561102444 +/- 0.0005722810634574451</t>
+          <t>0.0030286928799149624 +/- 0.0009519911194032477</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.0012221041445270365 +/- 0.00041499732603115066</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.0012221041445270365 +/- 0.0005844845908607566</t>
+          <t>0.0004782146652496988 +/- 0.0006034971674601753</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.000690754516471892 +/- 0.0006742070956668154</t>
+          <t>0.003985122210414427 +/- 0.0008316937217055613</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-0.00015940488841656997 +/- 0.00024349498910497378</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.003347502656748069 +/- 0.0005844845908607797</t>
+          <t>5.313496280551222e-05 +/- 0.0006485948786255812</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.000531349628055211 +/- 0.0014839787506661956</t>
+          <t>-0.00010626992561107995 +/- 0.0007049149395016883</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.0019659936238045073 +/- 0.0006742070956668267</t>
+          <t>0.0002656748140276166 +/- 0.000544471347819292</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0008970976253298013 +/- 0.0015484327969520796</t>
+          <t>-0.003060686015831149 +/- 0.0017309994160270932</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.006807387862796855 +/- 0.0012807030184181015</t>
+          <t>0.0010554089709762459 +/- 0.001635032547211568</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.00031662269129290044 +/- 0.0013801263145775226</t>
+          <t>0.0044327176781002505 +/- 0.0015866275861079512</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.0010026385224274237 +/- 0.0016084169555807904</t>
+          <t>-0.0015303430079155911 +/- 0.0008654997080135678</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.0016886543535619691 +/- 0.001330820075242041</t>
+          <t>0.003905013192612128 +/- 0.0014586042175287956</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.007598944591029033 +/- 0.0016720822710031432</t>
+          <t>0.005646437994722942 +/- 0.0020031929177944234</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>0.0004221635883904895 +/- 0.0005683551247635201</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0014248021108179243 +/- 0.0012498912171321436</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.010606860158311315 +/- 0.0024576529862153067</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.02105540897097624 +/- 0.0024348859092473414</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.00643799472295512 +/- 0.0013720316622691387</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-0.002058047493403736 +/- 0.0008970976253298091</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.003430079155672827 +/- 0.0017541709908806824</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.01424802110817941 +/- 0.004208422593641573</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.008601583113456457 +/- 0.002871507727791639</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.001372031662269102 +/- 0.0007537127629069024</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0006332453825857454 +/- 0.0010501186671309948</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.0006860158311345454 +/- 0.0004749340369393007</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.007071240105540888 +/- 0.0017691878220833937</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0002359966203165939</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.0024802110817942037 +/- 0.001002638522427454</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.0074406332453826 +/- 0.0006441454150782777</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>-0.0034828496042216607 +/- 0.001400158222841309</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.004010554089709783 +/- 0.0016720822710031425</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.0015303430079155911 +/- 0.0010929981623856609</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.0010554089709762238 +/- 0.000333749621125941</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0012664907651715128 +/- 0.0019345965994536482</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.0050659630606859855 +/- 0.0017691878220833896</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.002744063324538237 +/- 0.0012443088255991253</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.003482849604221616 +/- 0.0016384353241435344</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.0010554089709762459 +/- 0.000471993240633225</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.016833773087071256 +/- 0.0013234761165155187</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.010343007915567293 +/- 0.0018462116817452281</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.01097625329815305 +/- 0.0011987141627018945</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-0.0008970976253298013 +/- 0.0011330295806640481</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.0023746701846965924 +/- 0.0010081780039336635</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.010079155672823248 +/- 0.003636569320109764</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.0007915567282322233 +/- 0.0018318263807609251</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-0.0017414248021107802 +/- 0.0007844891159534814</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.005329815303430107 +/- 0.0009858333346844236</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0.002005277044854914 +/- 0.0014509474495902337</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0.0011609498680738794 +/- 0.0008106750129676795</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.0004221635883904895 +/- 0.00021108179419524476</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.004379947229551473 +/- 0.0024072812090674437</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.002480211081794226 +/- 0.00110817941952506</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.0022163588390501586 +/- 0.001488837570413305</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.0027968337730870487 +/- 0.00147474286147569</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.0007387862796833678 +/- 0.0005381550937828821</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.0004221635883904895 +/- 0.0005170426897695218</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.002005277044854903 +/- 0.0009672982997268442</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.004379947229551484 +/- 0.001566313675953126</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>-0.002427440633245348 +/- 0.0008893034061400076</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.0012664907651715352 +/- 0.0012532287163100756</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>5.277044854881119e-05 +/- 0.00028417756238176007</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.0016358839050131468 +/- 0.0005993570813509356</t>
+          <t>-0.00021108179419524476 +/- 0.0004221635883904895</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,217 +2826,217 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.004327176781002662 +/- 0.001198714162701912</t>
+          <t>0.007651715039577811 +/- 0.002019805721266989</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.0007387862796834011 +/- 0.0014775725593667586</t>
+          <t>0.00031662269129286715 +/- 0.0006332453825857342</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.0004221635883904895 +/- 0.00021108179419524476</t>
+          <t>-0.0006860158311345454 +/- 0.000337895738123096</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.0019525065963061027 +/- 0.0005303364443863494</t>
+          <t>0.0006332453825857343 +/- 0.0005683551247635201</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.00021108179419527807 +/- 0.0013391638565118282</t>
+          <t>-0.002849604221635893 +/- 0.0013391638565118196</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.0017941952506596581 +/- 0.0011367102495270826</t>
+          <t>0.0070712401055408654 +/- 0.001890920619226289</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.00010554089709762238 +/- 0.0003948978772320672</t>
+          <t>0.00031662269129286715 +/- 0.0004221635883904895</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.0004749340369393118 +/- 0.0013022651904224737</t>
+          <t>-0.0017414248021108357 +/- 0.0012498912171321512</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0006860158311345788 +/- 0.0009454603096131468</t>
+          <t>0.00955145118733508 +/- 0.0014051215784374035</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.0010026385224274127 +/- 0.0006441454150782777</t>
+          <t>-0.0037467018469657166 +/- 0.0009276198327834786</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-0.0008443271767809679 +/- 0.0019489377638648416</t>
+          <t>0.005171503957783629 +/- 0.0018401684194366775</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.021213720316622664 +/- 0.0016144652813486439</t>
+          <t>-0.006332453825857532 +/- 0.0019744893861604012</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.006807387862796865 +/- 0.0008654997080135233</t>
+          <t>-0.00036939313984171165 +/- 0.0011330295806640665</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0027968337730870816 +/- 0.0011811624952822943</t>
+          <t>0.003957783641160939 +/- 0.0017382236508707797</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0004087581368028822</t>
+          <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.0018997361477572916 +/- 0.0008243007573516325</t>
+          <t>0.007810026385224256 +/- 0.0015795915089283268</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0031134564643799712 +/- 0.0022069154265252273</t>
+          <t>-0.007071240105540921 +/- 0.002290504951367879</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.007282321899736132 +/- 0.0018249727140675998</t>
+          <t>-0.021319261213720332 +/- 0.0017848585250963265</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.0005277044854881119 +/- 0.0022138445343961</t>
+          <t>-0.004274406332453828 +/- 0.0018945987410043518</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.0008970976253297902 +/- 0.00024182457493169984</t>
+          <t>0.0003693931398416783 +/- 0.0004749340369393007</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
+          <t>-0.00221635883905017 +/- 0.0006591026911238426</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>-0.01187335092348285 +/- 0.0014403529355098833</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-0.010659630606860182 +/- 0.0016985199936074725</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-0.0029023746701847264 +/- 0.0016049505356987267</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-5.277044854882229e-05 +/- 0.0007254737247951229</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.005488126649076508 +/- 0.0013801263145775294</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.002163588390501314 +/- 0.0014051215784374068</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.0005804749340369231 +/- 0.0006860158311345455</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.008654353562005269 +/- 0.0008893034061399839</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-0.01298153034300793 +/- 0.0019201483270353766</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-0.027493403693931405 +/- 0.0018649706645986475</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>0.0023746701846965477 +/- 0.0016894786906155495</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.000333749621125941</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0.0032717678100263824 +/- 0.0011752536913625367</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0.0005804749340369231 +/- 0.0014442144784595262</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0.0017414248021108026 +/- 0.0010300380631104672</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>-0.0008443271767810123 +/- 0.0010340853795390902</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0.004960422163588352 +/- 0.0011846936316962284</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>0.009709762532981513 +/- 0.0018761360247631755</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>0.00021108179419524476 +/- 0.0004221635883904895</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
           <t>0.00026385224274405594 +/- 0.0003539949304748908</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>-0.007598944591029011 +/- 0.0016384353241435487</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>0.009920844327176803 +/- 0.00216036828395343</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>0.0016358839050132135 +/- 0.0013234761165155141</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>5.277044854881119e-05 +/- 0.0004383442671724455</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>0.0018469656992084692 +/- 0.0011621485776013424</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>0.00865435356200528 +/- 0.001977308073371529</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>-0.0006332453825857343 +/- 0.00021108179419524473</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.0011609498680739017 +/- 0.0009672982997268477</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>0.0037467018469657166 +/- 0.0016256381847756666</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-0.030290237467018442 +/- 0.0019913416637586364</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>0.005910290237467042 +/- 0.0020135919818827443</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0.00021108179419524476 +/- 0.00025852134488476094</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.001635883905013158 +/- 0.00109299816238563</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>-0.0011081794195250461 +/- 0.0016426788829839766</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0.0004221635883905228 +/- 0.001126868417100938</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0.006965699208443299 +/- 0.0017148366025617006</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>0.0011081794195250793 +/- 0.0012364511360274544</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>2.2204460492503132e-17 +/- 0.0013349984845037904</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>-0.00031662269129286715 +/- 0.000753712762906876</t>
-        </is>
-      </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.0006332453825857343 +/- 0.0003166226912928671</t>
+          <t>0.00021108179419524476 +/- 0.0004221635883904895</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,52 +3046,52 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.0013720316622690908 +/- 0.000675791476246192</t>
+          <t>0.00031662269129285604 +/- 0.0011609498680738644</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.0012664907651715241 +/- 0.0009498680738786446</t>
+          <t>0.003377308707124005 +/- 0.0010606728887726613</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0005277044854881119 +/- 0.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>-0.0010026385224274127 +/- 0.0005509396574622827</t>
+          <t>0.0003693931398416783 +/- 0.0005303364443863118</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.00015831134564641135 +/- 0.0011811624952822943</t>
+          <t>0.0006860158311345566 +/- 0.0011081794195250546</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.0016358839050131468 +/- 0.0006860158311345454</t>
+          <t>0.0012664907651714907 +/- 0.0017691878220834067</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0007915567282321678 +/- 0.00026385224274405594</t>
+          <t>0.0006332453825857343 +/- 0.0003948978772320672</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0032189973614775934 +/- 0.0006441454150782777</t>
+          <t>0.0034828496042216385 +/- 0.0009498680738786236</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.0006860158311345454 +/- 0.001474742861475684</t>
+          <t>0.009340369393139824 +/- 0.002071534187481852</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>0.00221635883905017 +/- 0.0007000791114206638</t>
+          <t>0.003693931398416872 +/- 0.0015654244827642458</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.00182806324110677 +/- 0.0013081227564104572</t>
+          <t>-3.3306690738754695e-17 +/- 0.0009631219708309311</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.0014822134387351472 +/- 0.0013071893829370432</t>
+          <t>0.0008893280632410683 +/- 0.00065545944473426</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.010918972332015853 +/- 0.0013878035479435058</t>
+          <t>0.006867588932806279 +/- 0.0009490796794614109</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.003112648221343828 +/- 0.0007670046786689566</t>
+          <t>0.0010375494071145908 +/- 0.000714270370296484</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.004594861660079097 +/- 0.0015155989772903116</t>
+          <t>0.0039525691699604185 +/- 0.0012692917567850802</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.013142292490118635 +/- 0.002907893076988577</t>
+          <t>0.01126482213438731 +/- 0.0007261333229594239</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00029644268774701164 +/- 0.00032772972236711905</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0011857707509881576 +/- 0.0006701907097949929</t>
+          <t>0.0039525691699604185 +/- 0.0012302272330028232</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.024160079051383433 +/- 0.003136087168489786</t>
+          <t>0.018330039525691677 +/- 0.0021245059288537457</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.02470355731225299 +/- 0.0026789410497482223</t>
+          <t>0.0186758893280632 +/- 0.002667984189723338</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.01304347826086959 +/- 0.001611611307341939</t>
+          <t>0.006521739130434745 +/- 0.0017648785671434497</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.00014822134387353357 +/- 0.0016393932829087978</t>
+          <t>-0.0013833992094862135 +/- 0.001428540740593018</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0015316205533597027 +/- 0.0014052828708822132</t>
+          <t>0.0009387351778655905 +/- 0.0009230010717524257</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.025642292490118613 +/- 0.004064917622940064</t>
+          <t>0.013883399209486124 +/- 0.004212373056728016</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.016798418972332065 +/- 0.0018618027353178401</t>
+          <t>0.003903162055335907 +/- 0.0009230010717524544</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.0016798418972332363 +/- 0.0011309805476541009</t>
+          <t>0.0007411067193675569 +/- 0.0014191113257258098</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.006373517786561311 +/- 0.0005611569511660292</t>
+          <t>0.006620553359683779 +/- 0.0015018462602342584</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.011808300395256942 +/- 0.001893652954223026</t>
+          <t>0.012401185770750944 +/- 0.0010925565408841764</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.008843873517786604 +/- 0.0014896060703242352</t>
+          <t>0.0062252964426876885 +/- 0.0012142495778107206</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.94071146245223e-05 +/- 0.00026606545489795547</t>
+          <t>4.9407114624500094e-05 +/- 0.0001482213438735003</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.01012845849802375 +/- 0.0018650776766973391</t>
+          <t>0.003112648221343839 +/- 0.0011491801728866445</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.004990118577075042 +/- 0.0011363636363636383</t>
+          <t>-0.006966403162055379 +/- 0.0017738461532624788</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.001679841897233214 +/- 0.0007717638019670577</t>
+          <t>-0.0010869565217391463 +/- 0.0004307212394802961</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0004940711462450342 +/- 0.0009110221795744089</t>
+          <t>0.0036067193675888955 +/- 0.0013081227564104249</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00034584980237156726 +/- 0.0006269060049629152</t>
+          <t>0.0023221343873517375 +/- 0.0008852012286150739</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>9.881422924903349e-05 +/- 0.000296442687747045</t>
+          <t>-0.00014822134387353357 +/- 0.00022641184263618222</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.013784584980237203 +/- 0.001828063241106732</t>
+          <t>0.008745059288537504 +/- 0.001836057724907305</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.00563241106719371 +/- 0.0014522666459188857</t>
+          <t>-0.0016798418972332363 +/- 0.0012538120099258672</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.001828063241106681 +/- 0.0015940974115515392</t>
+          <t>-0.009733201581027705 +/- 0.0014994062159578712</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.00474308300395262 +/- 0.0016116113073419201</t>
+          <t>-0.0030138339920949275 +/- 0.0016304347826087225</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.0007411067193675569 +/- 0.0007411067193675865</t>
+          <t>0.0005434782608695121 +/- 0.0001482213438735336</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.00039525691699608955 +/- 0.00019762845849804477</t>
+          <t>0.00044466403162052304 +/- 0.00034584980237153555</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.00197628458498027 +/- 0.0014656518749201167</t>
+          <t>-9.881422924903349e-05 +/- 0.0015276309124249282</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.0006422924901185456 +/- 0.0019520500261994383</t>
+          <t>-0.003853754940711507 +/- 0.0011857707509881595</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.00039525691699601186 +/- 0.00029644268774702275</t>
+          <t>-4.940711462451119e-05 +/- 0.0001482213438735336</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0004940711462450564</t>
+          <t>0.00029644268774702275 +/- 0.000503855683161346</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.0006916996047430568 +/- 0.0008893280632411003</t>
+          <t>0.005484189723320121 +/- 0.0012586698817052516</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0005434782608695233 +/- 0.001584882898453095</t>
+          <t>-0.003606719367588984 +/- 0.0014994062159578638</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.0014328063241106914 +/- 0.0006422924901185841</t>
+          <t>0.0016798418972331585 +/- 0.000739457981575875</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.0013339920948616801 +/- 0.0007004667430216335</t>
+          <t>0.0044960474308299745 +/- 0.0013878035479434894</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0026679841897232935 +/- 0.0014855035947008842</t>
+          <t>-0.0031126482213439167 +/- 0.001127738360722673</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0002964426877470561 +/- 0.0006327197863075884</t>
+          <t>0.0025691699604742714 +/- 0.0009580394975131168</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.002371541501976315 +/- 0.0013220442846106496</t>
+          <t>0.00044466403162053415 +/- 0.0012391241308284866</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0067687747035573564 +/- 0.001901371680325477</t>
+          <t>0.014871541501976237 +/- 0.0011363636363636498</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.006521739130434745 +/- 0.0008782800807624361</t>
+          <t>-9.881422924903349e-05 +/- 0.0007590064968249684</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.001136363636363602 +/- 0.0007004667430216374</t>
+          <t>-0.0014328063241107025 +/- 0.0006792355279084732</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4.940711462451119e-05 +/- 0.0001482213438735336</t>
+          <t>-1.1102230246251566e-17 +/- 0.00022095533374503725</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-9.881422924896688e-05 +/- 0.0007590064968249555</t>
+          <t>0.001828063241106681 +/- 0.0011277383607226482</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.006620553359683845 +/- 0.0017977673318834162</t>
+          <t>0.001185770750988091 +/- 0.0011523620345543987</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0015316205533597027 +/- 0.0011990771837462155</t>
+          <t>0.003063241106719328 +/- 0.0012845849802371526</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0016798418972332363 +/- 0.0011939768748611232</t>
+          <t>0.01773715415019759 +/- 0.0010699806238986171</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.002124505928853715 +/- 0.0008282141607826225</t>
+          <t>-0.0011857707509881688 +/- 0.0005501743441531491</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.00034584980237151175 +/- 0.00031635989315378205</t>
+          <t>0.00014822134387348918 +/- 0.0005434782608695545</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.00044466403162057855 +/- 0.00046610578715693536</t>
+          <t>0.013833992094861613 +/- 0.0007328259374600416</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.0038043478260869844 +/- 0.002760173463135073</t>
+          <t>0.005879446640316155 +/- 0.0013701012474172118</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.004644268774703597 +/- 0.0012341893277467279</t>
+          <t>-0.003507905138339984 +/- 0.001569405155560136</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,77 +3396,77 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.00044466403162053415 +/- 0.0006030906924769568</t>
+          <t>-0.0006916996047431123 +/- 0.0006701907097949897</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.002173913043478237 +/- 0.0008326234953731492</t>
+          <t>0.0020750988142292036 +/- 0.0009056473705446309</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.0010375494071145908 +/- 0.0015059042148348046</t>
+          <t>-0.003606719367588973 +/- 0.0015316205533596977</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.00034584980237151175 +/- 0.0007670046786689709</t>
+          <t>-4.94071146245334e-05 +/- 0.0005611569511660341</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.0008399209486166126 +/- 0.0007981963646938377</t>
+          <t>-0.0014328063241106914 +/- 0.00046610578715693536</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.002075098814229259 +/- 0.0013939462430499947</t>
+          <t>-0.001531620553359736 +/- 0.001199077183746214</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0.006966403162055402 +/- 0.0014052828708822007</t>
+          <t>0.00765810276679838 +/- 0.0014698097609331631</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0.0014328063241106914 +/- 0.000714270370296488</t>
+          <t>-0.002173913043478315 +/- 0.0007394579815759075</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.0006422924901185678 +/- 0.0004446640316205527</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.002865612648221305 +/- 0.0006170946638733523</t>
+          <t>-0.0027173913043478715 +/- 0.0007074022264464734</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.0027173913043477605 +/- 0.00039833289270249867</t>
+          <t>0.0008399209486165682 +/- 0.0007670046786689673</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0007905138339921236 +/- 0.0007056747459034489</t>
+          <t>0.000691699604743068 +/- 0.0005928853754940714</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.0008399209486165682 +/- 0.0012112303035702883</t>
+          <t>-0.0015316205533597027 +/- 0.00046610578715692945</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.0006422924901185456 +/- 0.0007670046786689672</t>
+          <t>-0.005434782608695709 +/- 0.0013440188249738462</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.004199604743082941 +/- 0.0011743937079055984</t>
+          <t>-0.001630434782608725 +/- 0.0009643884039497936</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.0003952569169960674 +/- 0.0007261333229594541</t>
+          <t>-0.0005928853754940788 +/- 0.0007590064968249554</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.00044466403162053415 +/- 0.000515825420400725</t>
+          <t>9.881422924896688e-05 +/- 0.0005321309097959048</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.0004940711462450454 +/- 0.0006987221157969718</t>
+          <t>0.0001482213438735003 +/- 0.00022641184263613135</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.007262845849802324 +/- 0.001127738360722673</t>
+          <t>-0.0001976284584980559 +/- 0.0010869565217391333</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.00034584980237151175 +/- 0.0004446640316205539</t>
+          <t>4.940711462447789e-05 +/- 0.00034584980237153555</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.004199604743082941 +/- 0.0008906994257569107</t>
+          <t>0.0007411067193675569 +/- 0.0005062722710454236</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0037055335968378955 +/- 0.0006720094124869191</t>
+          <t>-0.00014822134387354469 +/- 0.0009387351778656</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>0.0013339920948616912 +/- 0.0007344895626145468</t>
+          <t>-0.0004940711462450787 +/- 0.0004940711462450676</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.004891304347826031 +/- 0.0008961638906727819</t>
+          <t>-0.0008893280632411238 +/- 0.0008782800807624074</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.0007905138339920681 +/- 0.0009163654639817668</t>
+          <t>-0.0021739130434782817 +/- 0.0011733539611697658</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.002420948616600771 +/- 0.0008961638906727738</t>
+          <t>0.002470355731225249 +/- 0.00082673915665422</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.0025428413488114863 +/- 0.0005637390285895812</t>
+          <t>-0.0002211166390271524 +/- 0.0009638250842544771</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.026368159203980092 +/- 0.001731394114247181</t>
+          <t>-0.02023217247097846 +/- 0.0011382675667205035</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.0020453289110005436 +/- 0.0006080707573244859</t>
+          <t>-0.0013819789939193972 +/- 0.0006180397947760585</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0016583747927031434 +/- 0.0006055528551743104</t>
+          <t>0.0019347705914870006 +/- 0.0006180397947760585</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.002708678828081801 +/- 0.0009717189514232651</t>
+          <t>-0.007131011608623628 +/- 0.0007186290768380288</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.002211166390270858 +/- 0.0008913496681369279</t>
+          <t>-0.002211166390270969 +/- 0.0008563810605212602</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.527915975677145e-05 +/- 0.0001658374792703143</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0007739082365948002 +/- 0.0006155626714018791</t>
+          <t>-0.002266445550027707 +/- 0.0017559292619423925</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.03571033720287455 +/- 0.002086010200565334</t>
+          <t>0.01990049751243772 +/- 0.0013540573481388431</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.02857932559425095 +/- 0.002306539087343833</t>
+          <t>0.019402985074626778 +/- 0.001648209122816529</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.007352128247650603 +/- 0.001186893894614914</t>
+          <t>-0.005583195135434027 +/- 0.0012714206744057434</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0033167495854062867 +/- 0.0014415041249757035</t>
+          <t>-0.0002211166390271302 +/- 0.0007079186553270583</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.0014925373134328291 +/- 0.0007837173509539945</t>
+          <t>-0.0061912658927585126 +/- 0.001071902677151201</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.01907131011608626 +/- 0.003507069524723456</t>
+          <t>0.02542841348811493 +/- 0.0032889938707890884</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.012935323383084629 +/- 0.0023737877892298274</t>
+          <t>5.527915975671594e-05 +/- 0.001684881222125872</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.001990049751243772 +/- 0.0006633499170812573</t>
+          <t>-0.0021558872305141976 +/- 0.001295232118724149</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0012161415146489719 +/- 0.000644660242658405</t>
+          <t>-0.0031509121061360835 +/- 0.001212366622413555</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.002211166390270858 +/- 0.0006540718389275389</t>
+          <t>0.0059701492537313165 +/- 0.0013266998341625149</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.000995024875621886 +/- 0.0007739082365948002</t>
+          <t>-0.0008291873963516605 +/- 0.0007518778611794346</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.0001105583195135429 +/- 0.00022111663902708577</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.0008291873963515717 +/- 0.0014884369284506578</t>
+          <t>0.0036484245439469152 +/- 0.0014028278098893823</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.0017136539524599149 +/- 0.0013186136475264244</t>
+          <t>0.004919845218352659 +/- 0.0013641749783585416</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.0010503040353786574 +/- 0.0007991615420011551</t>
+          <t>0.0006080707573244859 +/- 0.0007186290768380288</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.002487562189054715 +/- 0.0009654090213694253</t>
+          <t>0.0026533996683250293 +/- 0.0013266998341625149</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.0030403537866224295 +/- 0.000710073663828915</t>
+          <t>0.00027639579878382394 +/- 0.001734920378825378</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0007186290768380288 +/- 0.0005555486799956244</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.0019347705914870006 +/- 0.00044567483406846394</t>
+          <t>0.004809286898839115 +/- 0.0008581633331265866</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.0030956329463792008 +/- 0.0008634880791494327</t>
+          <t>-0.001381978993919386 +/- 0.0008998795243836342</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.001990049751243772 +/- 0.0008981800336800357</t>
+          <t>-0.00016583747927036984 +/- 0.0008581633331266332</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.527915975677145e-05 +/- 0.0011449593796134818</t>
+          <t>-0.0036484245439470262 +/- 0.0014028278098893823</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.00027639579878385723 +/- 0.0005096486709393502</t>
+          <t>0.0012714206744057432 +/- 0.0005555486799956244</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0010503040353786574 +/- 0.000627850563383112</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.0008291873963515717 +/- 0.0006180397947760585</t>
+          <t>-0.0006633499170813461 +/- 0.0008124344088833391</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.000497512437810943 +/- 0.0012952321187241491</t>
+          <t>0.0007186290768380066 +/- 0.0012373150517191755</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.0007186290768380288 +/- 0.0003539593276635058</t>
+          <t>-0.0001105583195135651 +/- 0.0002211166390271302</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.001216141514649083 +/- 0.00033167495854062866</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0013266998341625146 +/- 0.0008634880791494327</t>
+          <t>0.002708678828081801 +/- 0.0008365254809519894</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>5.527915975677145e-05 +/- 0.000799161542001155</t>
+          <t>-0.0033167495854063977 +/- 0.0009574631329844497</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.0002211166390270858 +/- 0.0006633499170812574</t>
+          <t>0.0013266998341625146 +/- 0.0007498430053206453</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.0003869541182974001 +/- 0.0003539593276635058</t>
+          <t>0.0007186290768379955 +/- 0.0012617702830860834</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.002487562189054715 +/- 0.0005664428284112523</t>
+          <t>0.0028745163073521152 +/- 0.0005416229392555372</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.0007186290768380288 +/- 0.0008930621570703946</t>
+          <t>0.0024322830292979438 +/- 0.0007079186553270116</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.0010503040353786574 +/- 0.0007599628018168854</t>
+          <t>0.0021558872305140865 +/- 0.0011713443947162518</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.013211719181868486 +/- 0.00180738338576802</t>
+          <t>0.005638474295190687 +/- 0.0009183663751153165</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0006633499170812573 +/- 0.0004136713528771613</t>
+          <t>-4.4408920985006264e-17 +/- 0.0005527915975677588</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0014925373134328291 +/- 0.00025332093393896183</t>
+          <t>0.0024322830292979438 +/- 0.0005637390285895812</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.00016583747927031433 +/- 0.0003539593276635058</t>
+          <t>-0.0006633499170813573 +/- 0.0003316749585406509</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0014925373134328291 +/- 0.0006080707573244859</t>
+          <t>-0.000552791597567781 +/- 0.0008199224419122205</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.006467661691542259 +/- 0.0011608623548922004</t>
+          <t>0.0007739082365947891 +/- 0.0010832458785110936</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.013598673300165887 +/- 0.0009950248756218861</t>
+          <t>-0.003814262023217341 +/- 0.0015723010119765425</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.01299060254284139 +/- 0.002710934181368548</t>
+          <t>0.014372581536760576 +/- 0.0031562415530392777</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.527915975677145e-05 +/- 0.0001658374792703143</t>
+          <t>0.00044223327805416047 +/- 0.0006446602426584222</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.0001105583195135429 +/- 0.0002211166390270858</t>
+          <t>0.0012714206744057432 +/- 0.0006080707573244859</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.0008844665561083432 +/- 0.00027081146962776856</t>
+          <t>0.0010503040353786574 +/- 0.0005215025501413245</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.01000552791597572 +/- 0.0027244270934995525</t>
+          <t>0.017744610281923635 +/- 0.0016107022978809728</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.0009397457158651146 +/- 0.0007014139049446911</t>
+          <t>0.001271420674405732 +/- 0.000990407565902112</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,77 +3841,77 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>5.527915975677145e-05 +/- 0.00016583747927031433</t>
+          <t>-0.0001105583195135873 +/- 0.0006904364840684121</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.002211166390270858 +/- 0.0004944318358208468</t>
+          <t>0.00011055831951348739 +/- 0.0008492145658229922</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>0.000497512437810943 +/- 0.0005215025501413245</t>
+          <t>-0.0031509121061360835 +/- 0.0007837173509539946</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0003316749585406065 +/- 0.0007895443259859638</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.004643449419568802 +/- 0.0006633499170812573</t>
+          <t>0.0012714206744057432 +/- 0.0007437050330057297</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.007020453289109973 +/- 0.0008930621570703946</t>
+          <t>0.015809839690436634 +/- 0.0011648041738919503</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0.003980099502487544 +/- 0.001071902677151201</t>
+          <t>0.013322277501381919 +/- 0.0019846681117762473</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.002598120508568258 +/- 0.0007437050330057297</t>
+          <t>0.002100608070757315 +/- 0.000644660242658405</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-0.0005527915975677145 +/- 0.0</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.00027639579878385723 +/- 0.00044567483406846394</t>
+          <t>-0.0022664455500277293 +/- 0.00109027545181406</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.0008291873963515717 +/- 0.0008652557126864819</t>
+          <t>0.0036484245439469152 +/- 0.0009638250842544286</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0009397457158651146 +/- 0.0010503040353786574</t>
+          <t>0.007241569928137059 +/- 0.0011179518195774789</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.002266445550027629 +/- 0.0009397457158651146</t>
+          <t>0.00011055831951350958 +/- 0.0007333609265573375</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.0002211166390270858 +/- 0.0006155626714018791</t>
+          <t>-0.0001105583195135762 +/- 0.0004819125421272576</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.0010503040353786574 +/- 0.0007186290768380287</t>
+          <t>0.0014925373134328291 +/- 0.0007837173509539946</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.000497512437810943 +/- 0.0003869541182974001</t>
+          <t>0.0025428413488114863 +/- 0.0011907495427605263</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0007186290768380288 +/- 0.000497512437810943</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.0028745163073521152 +/- 0.00041367135287716136</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.002598120508568258 +/- 0.000656403653235924</t>
+          <t>0.0025428413488114863 +/- 0.0011648041738919503</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.00033167495854062866 +/- 0.0002708114696277686</t>
+          <t>0.0007186290768380288 +/- 0.0006080707573244859</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.0020453289110005436 +/- 0.0003539593276635058</t>
+          <t>-0.0007186290768381176 +/- 0.0006564036532359576</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.00033167495854062866 +/- 0.0002708114696277686</t>
+          <t>-0.0008291873963516716 +/- 0.0006656492304473554</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0007739082365948002 +/- 0.0004422332780541716</t>
+          <t>0.0006633499170812463 +/- 0.0005953747713802858</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0004944318358208468</t>
+          <t>0.0030403537866224295 +/- 0.00108465543783021</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-0.004367053620784944 +/- 0.0003869541182974001</t>
+          <t>-4.4408920985006264e-17 +/- 0.001398464415773782</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.0032614704256495155 +/- 0.0005771313714157271</t>
+          <t>-0.000552791597567781 +/- 0.0007817653744461989</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.012951807228915656 +/- 0.0010860094203204646</t>
+          <t>0.011385542168674722 +/- 0.0016705330872122909</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,392 +4001,392 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.010602409638554222 +/- 0.0025301204819277133</t>
+          <t>0.005060240963855445 +/- 0.0013253012048192615</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.007168674698795186 +/- 0.0023861810024504043</t>
+          <t>6.02409638554624e-05 +/- 0.0012182980973588309</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0053614457831325235 +/- 0.0016486665281209526</t>
+          <t>-0.00024096385542164976 +/- 0.0009409939368562282</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.007349397590361429 +/- 0.0017417870234700005</t>
+          <t>0.0040963855421687016 +/- 0.0011366242327779052</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.009879518072289161 +/- 0.0020552677240038477</t>
+          <t>0.009698795180722919 +/- 0.001558134597153898</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>-6.024096385540689e-05 +/- 0.0004216867469879434</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.005240963855421732 +/- 0.0008540630649854206</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.015361445783132588 +/- 0.00286698892392548</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.021867469879518108 +/- 0.0030246723399115993</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-0.0018674698795180355 +/- 0.0012764831385793291</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.005120481927710885 +/- 0.0012990276296896257</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-0.002228915662650577 +/- 0.0010098225671229086</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.00783132530120485 +/- 0.0019613036862770722</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.016265060240963903 +/- 0.0025699673503254933</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.0060843373493976284 +/- 0.0021118732702359146</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-0.0031927710843373093 +/- 0.0016398382637127919</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.004397590361445802 +/- 0.0011124208019650226</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>-0.0016867469879517593 +/- 0.0022346068663845107</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-0.00018072289156625398 +/- 0.0002760587768045517</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-0.007409638554216824 +/- 0.0021221584281697022</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.003373493975903652 +/- 0.0018508784934623277</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.0036144578313253573 +/- 0.0008519358809476661</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.0027710843373494275 +/- 0.0007714607514979228</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.001506024096385572 +/- 0.000980651843138548</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.0002409638554217164 +/- 0.0002951192461184915</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.00638554216867474 +/- 0.0010503370948290874</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.0009638554216867878 +/- 0.0019464451110124744</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-0.000963855421686699 +/- 0.0013789786918385104</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.0009036144578313587 +/- 0.0017921053952582497</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>-0.0007228915662650159 +/- 0.00036144578313250796</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.0002409638554217164 +/- 0.0002951192461184915</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.0021084337349397964 +/- 0.0018518585721613806</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-0.0038554216867469513 +/- 0.0013524062843761483</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>-0.0007228915662650159 +/- 0.0004508020947920135</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.0016867469879518482 +/- 0.0007524093973974188</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.0001807228915663095 +/- 0.0012360412366676703</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-0.000843373493975863 +/- 0.0005521175536091229</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.003313253012048223 +/- 0.0008625193411612469</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.0004216867469879149 +/- 0.0013211874818952682</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0021084337349397964 +/- 0.0009036144578313181</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-0.0033734939759035854 +/- 0.0015755056422436069</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>-0.005180722891566214 +/- 0.0019087927129825173</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>-0.00036144578313249685 +/- 0.000817148190737988</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0006626506024096756 +/- 0.0006842058247952137</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>-0.0008433734939758741 +/- 0.0006143397004328628</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.0047590361445783436 +/- 0.0013321291799696456</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.0015662650602410121 +/- 0.000901604189584073</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-0.006024096385542144 +/- 0.001373705331444748</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-0.0024698795180722486 +/- 0.0006842058247952109</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-0.000481927710843344 +/- 0.000240963855421672</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.0003012048192771455 +/- 0.0003012048192771455</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>-0.0009036144578313032 +/- 0.0008625193411612159</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>-0.012228915662650563 +/- 0.001572046789240951</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.0056626506024096915 +/- 0.001015198767852581</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-0.00048192771084333287 +/- 0.0005902384922368946</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.004457831325301242 +/- 0.0007714607514979192</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>-0.006144578313252968 +/- 0.0013143026644139425</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>-0.00060240963855418 +/- 0.0002694057804216449</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.0027108433734939984 +/- 0.000980651843138541</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-0.0033132530120481675 +/- 0.0015060240963855342</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>0.001566265060241001 +/- 0.0011804769844738097</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>0.008674698795180758 +/- 0.0013524062843761275</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.0024096385542168976 +/- 0.0011743125716637268</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.010602409638554267 +/- 0.000901604189584073</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0.0002409638554217164 +/- 0.0004819277108433911</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0.0009036144578313587 +/- 0.0007738091914858643</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>-0.0016867469879517706 +/- 0.00045080209479206096</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>0.009759036144578325 +/- 0.001519219302761259</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>0.00048192771084342166 +/- 0.00036144578313255236</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>0.0016265060240964301 +/- 0.0007153218124721563</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
           <t>-6.0240963855418e-05 +/- 0.00018072289156625398</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.01614457831325302 +/- 0.0029363994233624112</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.010421686746987957 +/- 0.0017676386447133946</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.0065662650602409615 +/- 0.0025048943236496246</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.004216867469879526 +/- 0.0021552462433732803</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.008674698795180725 +/- 0.0023049549963504667</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-0.004578313253012056 +/- 0.0025444231424027563</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0075903614457831226 +/- 0.0016209185598884002</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.005361445783132535 +/- 0.0031354249830537707</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0.002469879518072282 +/- 0.002779583613267315</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-0.011867469879518078 +/- 0.002800395011848048</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>-0.004638554216867474 +/- 0.0020526174743856255</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0.010361445783132528 +/- 0.00308113538615529</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>-0.0001204819277108471 +/- 0.0005251685474145297</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-0.01987951807228917 +/- 0.0015938260910027687</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0.008554216867469867 +/- 0.0016119383325614038</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.005602409638554217 +/- 0.0016835167002990496</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.0010843373493976017 +/- 0.00036144578313255236</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.002349397590361446 +/- 0.0013046028811872104</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.0001807228915662651 +/- 0.0005421686746987829</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.007891566265060235 +/- 0.001836114536641933</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>-0.009036144578313244 +/- 0.0016607287653120858</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>-0.003433734939759048 +/- 0.0011445783132530238</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.0022289156626506103 +/- 0.0024551426352186424</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>-0.00018072289156625398 +/- 0.0002760587768045517</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.001566265060240979 +/- 0.0006143397004328715</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>0.0074096385542168795 +/- 0.002556517490834086</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-0.0030120481927710884 +/- 0.0017870357800230617</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>-0.0012650602409638556 +/- 0.000828176330413698</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>0.0069277108433735135 +/- 0.0015534695130394727</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>-0.0003012048192771122 +/- 0.0018321573886440358</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0.0005421686746987731 +/- 0.00032440751850208136</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.0043975903614457915 +/- 0.0012360412366676703</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0013253012048192847 +/- 0.0022346068663845237</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.005361445783132535 +/- 0.001411490905284329</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-0.0037349397590361487 +/- 0.0017829697092709353</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>-0.005542168674698811 +/- 0.0035002021798395105</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>0.00042168674698794817 +/- 0.002156087972069073</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.0033734939759036187 +/- 0.0008604130636798834</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>-0.0011445783132530084 +/- 0.0005683121163889596</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0.007590361445783134 +/- 0.0018703824935253175</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0030722891566265067 +/- 0.001436971137575468</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-0.012409638554216885 +/- 0.0022891566265060208</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-0.008734939759036131 +/- 0.002854303069995704</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0002694057804216449</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0.0003012048192771011 +/- 0.00040410867063249217</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0.00018072289156625398 +/- 0.000895546310079418</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-0.019216867469879516 +/- 0.002324551973683718</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-0.010361445783132528 +/- 0.0019575996155749287</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>6.0240963855418e-05 +/- 0.00032440751850205864</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>-0.0005421686746987953 +/- 0.0009880252690877569</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>0.006325301204819278 +/- 0.0017921053952582552</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>-0.0005421686746988064 +/- 0.0007353346756466127</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-0.0001204819277108471 +/- 0.001341629966947</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-0.008373493975903612 +/- 0.0016265060240963829</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>0.002108433734939752 +/- 0.0018713523574709697</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>0.013734939759036146 +/- 0.0007025243246801631</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.007771084337349399 +/- 0.0015812535841453687</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.012228915662650608 +/- 0.001924884976948257</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>-0.004156626506024108 +/- 0.000911611201832615</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0.01807228915662651 +/- 0.001660728765312082</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>0.013915662650602423 +/- 0.0012182980973588398</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>0.021506024096385544 +/- 0.0012360412366676605</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.0006626506024096423 +/- 0.0011881375255009632</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>0.001927710843373498 +/- 0.0010708667972669464</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0.00036144578313251907 +/- 0.0003995933482355893</t>
-        </is>
-      </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.021265060240963862 +/- 0.0012934283466014354</t>
+          <t>0.014277108433734975 +/- 0.0017049363491668677</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0029518072289156706 +/- 0.000628934127042805</t>
+          <t>-0.000120481927710836 +/- 0.00024096385542167202</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.014638554216867472 +/- 0.0012063243611145184</t>
+          <t>0.004819277108433773 +/- 0.0009713563552166952</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.01072289156626508 +/- 0.0012286794008657279</t>
+          <t>0.012168674698795212 +/- 0.001257868254085611</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.0001807228915662651 +/- 0.0008955463100794307</t>
+          <t>-6.0240963855384686e-05 +/- 0.0005003990278866445</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.0053614457831325235 +/- 0.0015346673738382114</t>
+          <t>0.011024096385542225 +/- 0.0015949641319125093</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.02162650602409637 +/- 0.0014114909052843285</t>
+          <t>0.011746987951807253 +/- 0.0017511375727407893</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.005180722891566259 +/- 0.0018896851977539995</t>
+          <t>0.001385542168674736 +/- 0.0007153218124721731</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.005184393372528085 +/- 0.0012882919073430054</t>
+          <t>-0.0033137359700694423 +/- 0.001996957957484706</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.002298236237306228 +/- 0.0009869687500063894</t>
+          <t>0.0012827365045430584 +/- 0.0008684167188280075</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0031533939070016227 +/- 0.0008433850260854885</t>
+          <t>-0.003420630678781356 +/- 0.0006413682522715458</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0013361838588989761 +/- 0.0007652496559741474</t>
+          <t>-0.0014965259219668404 +/- 0.0013048162069196861</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.00026723677177979964 +/- 0.0008017103153394064</t>
+          <t>0.0018706574024586087 +/- 0.0006435913724634985</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.344735435598435e-05 +/- 0.0006948156066274721</t>
+          <t>0.0014430785676109558 +/- 0.0005879208979155474</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.00010689470871192431 +/- 0.00021378941742384862</t>
+          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.00614644575093537 +/- 0.0009635358833415233</t>
+          <t>0.00037413148049175726 +/- 0.0007577470271917646</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0009620523784072632 +/- 0.0010363826525742938</t>
+          <t>-0.006734366648850831 +/- 0.0013351144838906258</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.0010689470871191875 +/- 0.0020140506340370636</t>
+          <t>-0.008551576696953467 +/- 0.0019270717666830437</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.0005344735435595993 +/- 0.0008943452982726755</t>
+          <t>-0.004543025120256494 +/- 0.0017111502505165338</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.00080171031533941 +/- 0.0009022951906004222</t>
+          <t>-0.008551576696953445 +/- 0.0007170715053446556</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.0018172100481026244 +/- 0.0004898530940626146</t>
+          <t>-0.004596472474612467 +/- 0.001100548384926465</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.020149652592196664 +/- 0.0019129374845722163</t>
+          <t>0.01384286477819352 +/- 0.0021170820224840664</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.017049706039551072 +/- 0.0019775521111704926</t>
+          <t>-0.007482629609834268 +/- 0.0012647952502618052</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.0007482629609834368 +/- 0.0009620523784072521</t>
+          <t>-0.002191341528594304 +/- 0.0006070452534259902</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.009887760555852498 +/- 0.0016603126207385447</t>
+          <t>-0.006146445750935292 +/- 0.002059631092249879</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.0004275788348476639 +/- 0.0008551576696953555</t>
+          <t>0.0018706574024586087 +/- 0.0005975595877872047</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0024051309460181858 +/- 0.0004927602596094797</t>
+          <t>-0.0041154462854088416 +/- 0.0012431537519628983</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5.3447354355962154e-05 +/- 0.00044396706910307355</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00037413148049169064 +/- 0.0008959409200555952</t>
+          <t>-0.0001068947087118688 +/- 0.0010635889226153121</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0018706574024585753 +/- 0.0003585357526723278</t>
+          <t>0.00037413148049175726 +/- 0.0010966480239809246</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0005344735435595993</t>
+          <t>-0.0051843933725280065 +/- 0.000895940920055592</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+          <t>0.00048102618920369266 +/- 0.0007726794385249006</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0002137894174238375 +/- 0.000595164549741332</t>
+          <t>-0.0012292891501870073 +/- 0.0006346521692698055</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+          <t>3.3306690738754695e-17 +/- 0.0004140014266389327</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.00037413148049171286 +/- 0.0012431537519629128</t>
+          <t>5.344735435599546e-05 +/- 0.0012523115461101015</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.0038482095136290863 +/- 0.0017036213202040924</t>
+          <t>-0.005291288081239942 +/- 0.0010809058480041173</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5.3447354355962154e-05 +/- 0.0008088052351908881</t>
+          <t>-0.001389631213254905 +/- 0.0010473499701905771</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.003741314804917162 +/- 0.0010953448173126159</t>
+          <t>-0.0020309994655264064 +/- 0.0012373957138204581</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.00042757883484769723 +/- 0.00021378941742384862</t>
+          <t>-0.000106894708711891 +/- 0.00046594323287445157</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00021378941742384862 +/- 0.0002618374925476542</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.0023516835916622125 +/- 0.0006844601002066243</t>
+          <t>-0.0024051309460181415 +/- 0.001075607258017008</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.0010154997327632143 +/- 0.0013404528277909807</t>
+          <t>-0.003901656867985004 +/- 0.001331901207309164</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00048102618920355946 +/- 0.00016034206306785314</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0005879208979155615 +/- 0.00044396706910303615</t>
+          <t>0.0005344735435596215 +/- 0.00023902383511490173</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.0008551576696953722 +/- 0.00042757883484765836</t>
+          <t>-0.002672367717797919 +/- 0.0009855205192188933</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>5.344735435595105e-05 +/- 0.0007726794385248915</t>
+          <t>-0.0001068947087118799 +/- 0.0014695592821878762</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.0003206841261357729 +/- 0.0003545296408717875</t>
+          <t>0.0005344735435596215 +/- 0.00033803074934992447</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.0003206841261357507 +/- 0.0006413682522715107</t>
+          <t>-0.0012292891501870184 +/- 0.0009575880741404903</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.0021378941742383863 +/- 0.0008280028532779012</t>
+          <t>0.00181721004810268 +/- 0.0004898530940626026</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.0006948156066274747 +/- 0.0006781709000774636</t>
+          <t>-0.0010154997327631809 +/- 0.0013404528277909612</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.00646712987707111 +/- 0.0013615969217377955</t>
+          <t>-0.0033671833244254047 +/- 0.001512663997657399</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.010689470871191886 +/- 0.0015490514961186005</t>
+          <t>-0.02255478353821482 +/- 0.0026379396428119813</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.0006948156066274635 +/- 0.0009272769413627706</t>
+          <t>-0.0020844468198823797 +/- 0.0006070452534259941</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.001175841795831112 +/- 0.0006232979043126839</t>
+          <t>-0.009727418492784568 +/- 0.0016176104703817902</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.00016034206306788645 +/- 0.0002449265470313243</t>
+          <t>-0.0005344735435595327 +/- 0.0008280028532779155</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.000748262960983459 +/- 0.000427578834847675</t>
+          <t>-0.009139497594869006 +/- 0.0017144858292191894</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0006948156066274525 +/- 0.0011475633647025165</t>
+          <t>0.0021378941742384193 +/- 0.0007558597340315846</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0016034206306787646 +/- 0.0014140840786021347</t>
+          <t>-0.004489577765900532 +/- 0.0012234658623473428</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.007375734901122399 +/- 0.0014301537317220284</t>
+          <t>-0.007482629609834268 +/- 0.002083761484726648</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-0.00016034206306788645 +/- 0.0002449265470313243</t>
+          <t>-0.0004275788348476306 +/- 0.0007482629609834289</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>-0.00026723677177981076 +/- 0.00035853575267235255</t>
+          <t>-0.0004275788348476417 +/- 0.0005236749850952631</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
+          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.01475146980224481 +/- 0.0014965259219668577</t>
+          <t>-0.005986103687867417 +/- 0.002915698919719051</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.0021378941742383863 +/- 0.0009257353327465843</t>
+          <t>-0.0032068412613575183 +/- 0.0013091874627382167</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-0.00037413148049173504 +/- 0.0002449265470313243</t>
+          <t>-0.0016568679850347157 +/- 0.00028782281171217444</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0.00026723677177979964 +/- 0.00043090634678239343</t>
+          <t>-0.0004275788348476417 +/- 0.0006232979043126839</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.00010689470871192431 +/- 0.0008551576696953528</t>
+          <t>-0.001068947087119143 +/- 0.0006760614986998226</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+          <t>-5.344735435593995e-05 +/- 0.0002878228117121373</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0005879208979155725 +/- 0.0005042213325524679</t>
+          <t>-0.01010154997327628 +/- 0.0008433850260854828</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0.0008017103153393768 +/- 0.0007652496559741475</t>
+          <t>-0.005291288081239953 +/- 0.0016114177906661005</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.01902725815072156 +/- 0.001659452132149656</t>
+          <t>-0.0072688401924104196 +/- 0.0013351144838906204</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-0.00021378941742384862 +/- 0.0003545296408717875</t>
+          <t>0.0016034206306788311 +/- 0.0004140014266389327</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.00037413148049174615 +/- 0.0006346521692698055</t>
+          <t>0.0034740780331373954 +/- 0.0013782786700403712</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0005854864323946291</t>
+          <t>-0.0008017103153393545 +/- 0.0006865436974166258</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-0.00048102618920365937 +/- 0.00028782281171217444</t>
+          <t>0.00042757883484769723 +/- 0.00021378941742384862</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-0.00026723677177981076 +/- 0.00026723677177981076</t>
+          <t>0.0029930518439337693 +/- 0.0005450582056219186</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>-0.0013361838588989872 +/- 0.0007652496559741436</t>
+          <t>0.001496525921966907 +/- 0.0007482629609834336</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.00010689470871192431 +/- 0.00039996337645902035</t>
+          <t>0.007001603420630742 +/- 0.0008433850260854885</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.00016034206306787536 +/- 0.0003422300501032939</t>
+          <t>0.00026723677177981076 +/- 0.00035853575267235255</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.0009620523784072521 +/- 0.0005236749850952608</t>
+          <t>0.00037413148049173504 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.00016034206306786425 +/- 0.0005371392635553559</t>
+          <t>0.00021378941742384862 +/- 0.0003545296408717875</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.0008017103153393768 +/- 0.0007269626140425072</t>
+          <t>0.00160342063067882 +/- 0.0011211211631963294</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0009620523784073187 +/- 0.0005236749850953084</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.0003206841261357618 +/- 0.0006844601002066259</t>
+          <t>0.0004275788348477194 +/- 0.0005756456234243118</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>-0.00042757883484769723 +/- 0.0006232979043127314</t>
+          <t>0.0027792624265099096 +/- 0.0006232979043127048</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.0003206841261357729 +/- 0.0002618374925476542</t>
+          <t>0.00042757883484769723 +/- 0.0004659432328744949</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>0.0013361838588989649 +/- 0.0008017103153393953</t>
+          <t>0.0009086050240513565 +/- 0.0005371392635553935</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.0016034206306787646 +/- 0.0007170715053446886</t>
+          <t>0.0023516835916622346 +/- 0.00042757883484767777</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.00090860502405129 +/- 0.0004810261892036125</t>
+          <t>0.0006413682522715458 +/- 0.00039996337645902035</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0003206841261357729 +/- 0.0002618374925476542</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,27 +4891,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.3447354355962154e-05 +/- 0.00044396706910307355</t>
+          <t>-0.0012827365045430805 +/- 0.0005450582056219013</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.0005344735435595993 +/- 0.00033803074934988934</t>
+          <t>-0.00160342063067882 +/- 0.0005344735435595771</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.00037413148049173504 +/- 0.0002449265470313243</t>
+          <t>0.0008551576696952945 +/- 0.0004898530940626292</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0002137894174238375 +/- 0.000427578834847675</t>
+          <t>-0.0017637626937467067 +/- 0.001015499732763212</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.00026723677177979964 +/- 0.0004927602596094616</t>
+          <t>-0.0019241047568145596 +/- 0.0009007108255666891</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4921,402 +4921,402 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0013896312132549605 +/- 0.0004898530940626001</t>
+          <t>0.0008017103153393435 +/- 0.0010756072580169972</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.00026723677177981076 +/- 0.00035853575267235255</t>
+          <t>-0.002137894174238442 +/- 0.0012187871994646</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.0003206841261357618 +/- 0.00042757883484767777</t>
+          <t>-0.001977552111170544 +/- 0.0011963136977872421</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.0003206841261357729 +/- 0.00035452964087178746</t>
+          <t>0.0015499732763228024 +/- 0.0006070452534260078</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0006948156066274635 +/- 0.00034223005010327484</t>
+          <t>-0.001068947087119243 +/- 0.0007170715053446638</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00047804767022980346</t>
+          <t>-0.0009620523784073298 +/- 0.00057564562342432</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.00037413148049171286 +/- 0.0009575880741404989</t>
+          <t>0.0036344200962051933 +/- 0.0013048162069196844</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.0022982362373062727 +/- 0.0016220193378400439</t>
+          <t>0.0009620523784072299 +/- 0.0008551576696953625</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0010154997327632477 +/- 0.0006070452534259941</t>
+          <t>0.0032602886157134803 +/- 0.0010809058480041047</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.0011223944414751163 +/- 0.0003741314804917002</t>
+          <t>-0.0021378941742384193 +/- 0.00114631804326708</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.00021378941742384862 +/- 0.0002618374925476542</t>
+          <t>-0.0001068947087119687 +/- 0.0007090592817435265</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.00048102618920364826 +/- 0.00028782281171215173</t>
+          <t>-0.002084446819882446 +/- 0.0003741314804916922</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0013896312132549715 +/- 0.0013351144838906295</t>
+          <t>0.005130946018172056 +/- 0.001246595808625405</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.00016034206306787536 +/- 0.0004174371820366974</t>
+          <t>-0.0014430785676109558 +/- 0.0005371392635553647</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>-4.4408920985006264e-17 +/- 0.0005344735435595772</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-0.0001068947087119465 +/- 0.00039996337645898473</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.00042757883484769723 +/- 0.00039996337645902035</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0001068947087119021 +/- 0.0002137894174238042</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-0.000641368252271557 +/- 0.0009501009532138255</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-0.0043826830571886966 +/- 0.0004659432328744643</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>-0.0009620523784073187 +/- 0.0003206841261357729</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-0.0020309994655264728 +/- 0.0005236749850952676</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.0004275788348476084 +/- 0.0002137894174238042</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-0.0018172100481026576 +/- 0.0007249951879342768</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.004222340994120821 +/- 0.0006524081034598363</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>5.344735435592884e-05 +/- 0.0003741314804916922</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>0.0011758417958310564 +/- 0.0003206841261357729</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>-0.002084446819882446 +/- 0.0005042213325524467</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.0001068947087119021 +/- 0.0002137894174238042</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.00037413148049174615 +/- 0.0005371392635553746</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.0021913415285943596 +/- 0.0005042213325524526</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>-0.0009620523784073076 +/- 0.0005756456234243261</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-0.0019775521111705108 +/- 0.0007190606118158059</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.0020309994655264172 +/- 0.0005236749850952676</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>5.344735435593995e-05 +/- 0.00044396706910303615</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.0005879208979154837 +/- 0.00028782281171215173</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>-0.0009086050240513677 +/- 0.0008297260660748441</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>-0.002084446819882446 +/- 0.0010266901503099258</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-0.0008551576696953945 +/- 0.0007999267529180036</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.006253340459647183 +/- 0.0016220193378400321</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.0011758417958310674 +/- 0.00046594323287446686</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.0010154997327631587 +/- 0.0006070452534260058</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.007856761090325981 +/- 0.001288291907343016</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.000106894708711891 +/- 0.00085515766969535</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-0.00042757883484769723 +/- 0.00021378941742384862</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>-0.0003206841261357951 +/- 0.0007999267529180021</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>-0.0009620523784073076 +/- 0.0005756456234243261</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.00026723677177974413 +/- 0.00035853575267230295</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-0.00026723677177982187 +/- 0.0003585357526723278</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-0.0009086050240513343 +/- 0.0007190606118158044</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-0.0002137894174238597 +/- 0.0004898530940626194</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-0.0008017103153394323 +/- 0.00035853575267235255</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.0006413682522714681 +/- 0.000465943232874449</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.0017637626937466178 +/- 0.0005879208979155493</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>-0.000694815606627508 +/- 0.0003422300501033234</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0.0007482629609833924 +/- 0.0005951645497413061</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>-0.0015499732763228692 +/- 0.0006070452534259941</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>0.0011223944414750942 +/- 0.00044396706910307355</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>0.00048102618920358163 +/- 0.0003741314804916922</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>-0.00042757883484769723 +/- 0.00021378941742384862</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>-0.000267236771779833 +/- 0.0004927602596094435</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>-0.00042757883484769723 +/- 0.00021378941742384862</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>0.0004275788348476195 +/- 0.0003206841261357285</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>-0.000320684126135784 +/- 0.0003545296408717607</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
           <t>-0.00021378941742384862 +/- 0.0002618374925476542</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.0003206841261357729 +/- 0.0002618374925476542</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.00016034206306787536 +/- 0.00048102618920363834</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>-0.0006413682522715014 +/- 0.0005236749850952609</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>-0.0009620523784072743 +/- 0.0005756456234242993</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.00023902383511490173</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.00047804767022980346</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-0.00048102618920363714 +/- 0.0003741314804917001</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.0014965259219668404 +/- 0.00046594323287447195</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>-5.3447354355962154e-05 +/- 0.00028782281171217444</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>-0.00010689470871192431 +/- 0.00039996337645902035</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>1.1102230246251566e-17 +/- 0.0005344735435595994</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.0003206841261357729 +/- 0.0002618374925476542</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-0.0004275788348476861 +/- 0.0003206841261357507</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0.0009620523784072965 +/- 0.0005236749850952699</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>-0.00010689470871192431 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>-0.0002137894174238264 +/- 0.0005951645497413161</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>-0.00010689470871192431 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>-0.00026723677177981076 +/- 0.00035853575267235255</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>-0.0010689470871191654 +/- 0.000676061498699805</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-0.0005344735435596105 +/- 0.0002390238351148769</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>0.006306787814003223 +/- 0.0013265284495981575</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.00042757883484769723 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.0041688936397648365 +/- 0.0011413231696452372</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-0.0014430785676108671 +/- 0.0004174371820367215</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>-0.0006948156066274747 +/- 0.00024492654703127343</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.0003206841261357729 +/- 0.0002618374925476542</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-0.0004275788348476861 +/- 0.0003206841261357507</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-0.00016034206306788645 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-0.00042757883484769723 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>-0.00026723677177981076 +/- 0.00026723677177981076</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>0.0006413682522715458 +/- 0.00039996337645902035</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>0.00037413148049173504 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>-0.00016034206306788645 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>-5.3447354355962154e-05 +/- 0.00028782281171217444</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>-5.3447354355962154e-05 +/- 0.00028782281171217444</t>
-        </is>
-      </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0002137894174238153 +/- 0.0003545296408717406</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>-0.0002137894174238375 +/- 0.0003545296408717607</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
     </row>
